--- a/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0002T0006Z000C1N32_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0002T0006Z000C1N32_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>47.77517015049275</v>
+        <v>7.763465149455071</v>
       </c>
       <c r="D2" t="n">
-        <v>49.08582930570472</v>
+        <v>7.976447262177017</v>
       </c>
       <c r="E2" t="n">
-        <v>27.14391592219756</v>
+        <v>4.410886337357105</v>
       </c>
       <c r="F2" t="n">
-        <v>27.78659611813658</v>
+        <v>4.515321869197194</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>4.694323023532001</v>
+        <v>0.7628274913239502</v>
       </c>
       <c r="D3" t="n">
-        <v>4.500269947503202</v>
+        <v>0.7312938664692703</v>
       </c>
       <c r="E3" t="n">
-        <v>27.14391592219756</v>
+        <v>4.410886337357105</v>
       </c>
       <c r="F3" t="n">
-        <v>27.78659611813658</v>
+        <v>4.515321869197194</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>84.6209995923644</v>
+        <v>13.75091243375921</v>
       </c>
       <c r="D4" t="n">
-        <v>85.8662185909126</v>
+        <v>13.9532605210233</v>
       </c>
       <c r="E4" t="n">
-        <v>27.14391592219756</v>
+        <v>4.410886337357105</v>
       </c>
       <c r="F4" t="n">
-        <v>27.78659611813658</v>
+        <v>4.515321869197194</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>29.48765022955347</v>
+        <v>4.791743162302439</v>
       </c>
       <c r="D5" t="n">
-        <v>28.71242955282653</v>
+        <v>4.665769802334311</v>
       </c>
       <c r="E5" t="n">
-        <v>27.14391592219756</v>
+        <v>4.410886337357105</v>
       </c>
       <c r="F5" t="n">
-        <v>27.78659611813658</v>
+        <v>4.515321869197194</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>22.72722722869093</v>
+        <v>3.693174424662276</v>
       </c>
       <c r="D6" t="n">
-        <v>22.57204421998959</v>
+        <v>3.667957185748309</v>
       </c>
       <c r="E6" t="n">
-        <v>27.14391592219756</v>
+        <v>4.410886337357105</v>
       </c>
       <c r="F6" t="n">
-        <v>27.78659611813658</v>
+        <v>4.515321869197194</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
